--- a/data/simple-nonuniform-geometry.xlsx
+++ b/data/simple-nonuniform-geometry.xlsx
@@ -10,7 +10,6 @@
     <sheet name="Points" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Lines" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rectangles" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Stairs Locations" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +454,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -469,7 +468,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="B3" t="n">
         <v>2</v>
@@ -483,7 +482,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="B4" t="n">
         <v>7</v>
@@ -497,7 +496,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="B5" t="n">
         <v>12</v>
@@ -511,7 +510,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="B6" t="n">
         <v>17</v>
@@ -525,7 +524,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
@@ -539,7 +538,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="B8" t="n">
         <v>2</v>
@@ -553,7 +552,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="B9" t="n">
         <v>7</v>
@@ -567,7 +566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="B10" t="n">
         <v>12</v>
@@ -581,7 +580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>410</v>
       </c>
       <c r="B11" t="n">
         <v>17</v>
@@ -595,7 +594,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -609,7 +608,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="B13" t="n">
         <v>2</v>
@@ -623,7 +622,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="B14" t="n">
         <v>7</v>
@@ -637,7 +636,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>320</v>
       </c>
       <c r="B15" t="n">
         <v>12</v>
@@ -651,7 +650,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>420</v>
       </c>
       <c r="B16" t="n">
         <v>17</v>
@@ -665,7 +664,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -679,7 +678,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -693,7 +692,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="B19" t="n">
         <v>7</v>
@@ -707,7 +706,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="B20" t="n">
         <v>12</v>
@@ -721,7 +720,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="B21" t="n">
         <v>17</v>
@@ -735,7 +734,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="B22" t="n">
         <v>0</v>
@@ -749,7 +748,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="B23" t="n">
         <v>2</v>
@@ -763,7 +762,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="B24" t="n">
         <v>7</v>
@@ -777,7 +776,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>340</v>
       </c>
       <c r="B25" t="n">
         <v>12</v>
@@ -791,7 +790,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>440</v>
       </c>
       <c r="B26" t="n">
         <v>17</v>
@@ -805,7 +804,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="B27" t="n">
         <v>0</v>
@@ -819,7 +818,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="B28" t="n">
         <v>2</v>
@@ -833,7 +832,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="B29" t="n">
         <v>7</v>
@@ -847,7 +846,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1004</v>
+        <v>301</v>
       </c>
       <c r="B30" t="n">
         <v>12</v>
@@ -861,7 +860,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1005</v>
+        <v>401</v>
       </c>
       <c r="B31" t="n">
         <v>17</v>
@@ -875,7 +874,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="B32" t="n">
         <v>0</v>
@@ -889,7 +888,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="B33" t="n">
         <v>2</v>
@@ -903,7 +902,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="B34" t="n">
         <v>7</v>
@@ -917,7 +916,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="B35" t="n">
         <v>12</v>
@@ -931,7 +930,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1010</v>
+        <v>411</v>
       </c>
       <c r="B36" t="n">
         <v>17</v>
@@ -945,7 +944,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="B37" t="n">
         <v>0</v>
@@ -959,7 +958,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
@@ -973,7 +972,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="B39" t="n">
         <v>7</v>
@@ -987,7 +986,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="B40" t="n">
         <v>12</v>
@@ -1001,7 +1000,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1015</v>
+        <v>421</v>
       </c>
       <c r="B41" t="n">
         <v>17</v>
@@ -1015,7 +1014,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="B42" t="n">
         <v>0</v>
@@ -1029,7 +1028,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="B43" t="n">
         <v>2</v>
@@ -1043,7 +1042,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="B44" t="n">
         <v>7</v>
@@ -1057,7 +1056,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="B45" t="n">
         <v>12</v>
@@ -1071,7 +1070,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1020</v>
+        <v>431</v>
       </c>
       <c r="B46" t="n">
         <v>17</v>
@@ -1085,7 +1084,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1021</v>
+        <v>41</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
@@ -1099,7 +1098,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1022</v>
+        <v>141</v>
       </c>
       <c r="B48" t="n">
         <v>2</v>
@@ -1113,7 +1112,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1023</v>
+        <v>241</v>
       </c>
       <c r="B49" t="n">
         <v>7</v>
@@ -1127,7 +1126,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1024</v>
+        <v>341</v>
       </c>
       <c r="B50" t="n">
         <v>12</v>
@@ -1141,7 +1140,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1025</v>
+        <v>441</v>
       </c>
       <c r="B51" t="n">
         <v>17</v>
@@ -1155,7 +1154,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2001</v>
+        <v>2</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -1169,7 +1168,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2002</v>
+        <v>102</v>
       </c>
       <c r="B53" t="n">
         <v>2</v>
@@ -1183,7 +1182,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2003</v>
+        <v>202</v>
       </c>
       <c r="B54" t="n">
         <v>7</v>
@@ -1197,7 +1196,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2004</v>
+        <v>302</v>
       </c>
       <c r="B55" t="n">
         <v>12</v>
@@ -1211,7 +1210,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2005</v>
+        <v>402</v>
       </c>
       <c r="B56" t="n">
         <v>17</v>
@@ -1225,7 +1224,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="B57" t="n">
         <v>0</v>
@@ -1239,7 +1238,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="B58" t="n">
         <v>2</v>
@@ -1253,7 +1252,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="B59" t="n">
         <v>7</v>
@@ -1267,7 +1266,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="B60" t="n">
         <v>12</v>
@@ -1281,7 +1280,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2010</v>
+        <v>412</v>
       </c>
       <c r="B61" t="n">
         <v>17</v>
@@ -1295,7 +1294,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="B62" t="n">
         <v>0</v>
@@ -1309,7 +1308,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="B63" t="n">
         <v>2</v>
@@ -1323,7 +1322,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="B64" t="n">
         <v>7</v>
@@ -1337,7 +1336,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="B65" t="n">
         <v>12</v>
@@ -1351,7 +1350,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2015</v>
+        <v>422</v>
       </c>
       <c r="B66" t="n">
         <v>17</v>
@@ -1365,7 +1364,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -1379,7 +1378,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="B68" t="n">
         <v>2</v>
@@ -1393,7 +1392,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="B69" t="n">
         <v>7</v>
@@ -1407,7 +1406,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="B70" t="n">
         <v>12</v>
@@ -1421,7 +1420,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2020</v>
+        <v>432</v>
       </c>
       <c r="B71" t="n">
         <v>17</v>
@@ -1435,7 +1434,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2021</v>
+        <v>42</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -1449,7 +1448,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022</v>
+        <v>142</v>
       </c>
       <c r="B73" t="n">
         <v>2</v>
@@ -1463,7 +1462,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2023</v>
+        <v>242</v>
       </c>
       <c r="B74" t="n">
         <v>7</v>
@@ -1477,7 +1476,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2024</v>
+        <v>342</v>
       </c>
       <c r="B75" t="n">
         <v>12</v>
@@ -1491,7 +1490,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>442</v>
       </c>
       <c r="B76" t="n">
         <v>17</v>
@@ -1505,7 +1504,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3001</v>
+        <v>3</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -1519,7 +1518,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3002</v>
+        <v>103</v>
       </c>
       <c r="B78" t="n">
         <v>2</v>
@@ -1533,7 +1532,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="B79" t="n">
         <v>7</v>
@@ -1547,7 +1546,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3004</v>
+        <v>303</v>
       </c>
       <c r="B80" t="n">
         <v>12</v>
@@ -1561,7 +1560,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3005</v>
+        <v>403</v>
       </c>
       <c r="B81" t="n">
         <v>17</v>
@@ -1575,7 +1574,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -1589,7 +1588,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="B83" t="n">
         <v>2</v>
@@ -1603,7 +1602,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="B84" t="n">
         <v>7</v>
@@ -1617,7 +1616,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="B85" t="n">
         <v>12</v>
@@ -1631,7 +1630,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3010</v>
+        <v>413</v>
       </c>
       <c r="B86" t="n">
         <v>17</v>
@@ -1645,7 +1644,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -1659,7 +1658,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="B88" t="n">
         <v>2</v>
@@ -1673,7 +1672,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="B89" t="n">
         <v>7</v>
@@ -1687,7 +1686,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="B90" t="n">
         <v>12</v>
@@ -1701,7 +1700,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3015</v>
+        <v>423</v>
       </c>
       <c r="B91" t="n">
         <v>17</v>
@@ -1715,7 +1714,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -1729,7 +1728,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="B93" t="n">
         <v>2</v>
@@ -1743,7 +1742,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="B94" t="n">
         <v>7</v>
@@ -1757,7 +1756,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="B95" t="n">
         <v>12</v>
@@ -1771,7 +1770,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3020</v>
+        <v>433</v>
       </c>
       <c r="B96" t="n">
         <v>17</v>
@@ -1785,7 +1784,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>3021</v>
+        <v>43</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -1799,7 +1798,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3022</v>
+        <v>143</v>
       </c>
       <c r="B98" t="n">
         <v>2</v>
@@ -1813,7 +1812,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3023</v>
+        <v>243</v>
       </c>
       <c r="B99" t="n">
         <v>7</v>
@@ -1827,7 +1826,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3024</v>
+        <v>343</v>
       </c>
       <c r="B100" t="n">
         <v>12</v>
@@ -1841,7 +1840,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3025</v>
+        <v>443</v>
       </c>
       <c r="B101" t="n">
         <v>17</v>
@@ -1855,7 +1854,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4001</v>
+        <v>4</v>
       </c>
       <c r="B102" t="n">
         <v>0</v>
@@ -1869,7 +1868,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4002</v>
+        <v>104</v>
       </c>
       <c r="B103" t="n">
         <v>2</v>
@@ -1883,7 +1882,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4003</v>
+        <v>204</v>
       </c>
       <c r="B104" t="n">
         <v>7</v>
@@ -1897,7 +1896,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4004</v>
+        <v>304</v>
       </c>
       <c r="B105" t="n">
         <v>12</v>
@@ -1911,7 +1910,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4005</v>
+        <v>404</v>
       </c>
       <c r="B106" t="n">
         <v>17</v>
@@ -1925,7 +1924,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4006</v>
+        <v>14</v>
       </c>
       <c r="B107" t="n">
         <v>0</v>
@@ -1939,7 +1938,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="B108" t="n">
         <v>2</v>
@@ -1953,7 +1952,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="B109" t="n">
         <v>7</v>
@@ -1967,7 +1966,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="B110" t="n">
         <v>12</v>
@@ -1981,7 +1980,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4010</v>
+        <v>414</v>
       </c>
       <c r="B111" t="n">
         <v>17</v>
@@ -1995,7 +1994,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4011</v>
+        <v>24</v>
       </c>
       <c r="B112" t="n">
         <v>0</v>
@@ -2009,7 +2008,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="B113" t="n">
         <v>2</v>
@@ -2023,7 +2022,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="B114" t="n">
         <v>7</v>
@@ -2037,7 +2036,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="B115" t="n">
         <v>12</v>
@@ -2051,7 +2050,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4015</v>
+        <v>424</v>
       </c>
       <c r="B116" t="n">
         <v>17</v>
@@ -2065,7 +2064,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4016</v>
+        <v>34</v>
       </c>
       <c r="B117" t="n">
         <v>0</v>
@@ -2079,7 +2078,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="B118" t="n">
         <v>2</v>
@@ -2093,7 +2092,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="B119" t="n">
         <v>7</v>
@@ -2107,7 +2106,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="B120" t="n">
         <v>12</v>
@@ -2121,7 +2120,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4020</v>
+        <v>434</v>
       </c>
       <c r="B121" t="n">
         <v>17</v>
@@ -2135,7 +2134,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4021</v>
+        <v>44</v>
       </c>
       <c r="B122" t="n">
         <v>0</v>
@@ -2149,7 +2148,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4022</v>
+        <v>144</v>
       </c>
       <c r="B123" t="n">
         <v>2</v>
@@ -2163,7 +2162,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4023</v>
+        <v>244</v>
       </c>
       <c r="B124" t="n">
         <v>7</v>
@@ -2177,7 +2176,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>4024</v>
+        <v>344</v>
       </c>
       <c r="B125" t="n">
         <v>12</v>
@@ -2191,7 +2190,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4025</v>
+        <v>444</v>
       </c>
       <c r="B126" t="n">
         <v>17</v>
@@ -2214,7 +2213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:E261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2233,2865 +2232,4955 @@
           <t>point-2</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>sec-rotation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1001</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>3100</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C3" t="n">
-        <v>1002</v>
+        <v>101</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>3200</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>200</v>
       </c>
       <c r="C4" t="n">
-        <v>1003</v>
+        <v>201</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>3300</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="C5" t="n">
-        <v>1004</v>
+        <v>301</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>3400</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>400</v>
       </c>
       <c r="C6" t="n">
-        <v>1005</v>
+        <v>401</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>3010</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>1006</v>
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>3110</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>1007</v>
+        <v>111</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>3210</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>210</v>
       </c>
       <c r="C9" t="n">
-        <v>1008</v>
+        <v>211</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>3310</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="C10" t="n">
-        <v>1009</v>
+        <v>311</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>3410</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>410</v>
       </c>
       <c r="C11" t="n">
-        <v>1010</v>
+        <v>411</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>3020</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>1011</v>
+        <v>21</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>3120</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="C13" t="n">
-        <v>1012</v>
+        <v>121</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>3220</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>220</v>
       </c>
       <c r="C14" t="n">
-        <v>1013</v>
+        <v>221</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>3320</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>320</v>
       </c>
       <c r="C15" t="n">
-        <v>1014</v>
+        <v>321</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>3420</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>420</v>
       </c>
       <c r="C16" t="n">
-        <v>1015</v>
+        <v>421</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>3030</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C17" t="n">
-        <v>1016</v>
+        <v>31</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>3130</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="C18" t="n">
-        <v>1017</v>
+        <v>131</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>3230</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>230</v>
       </c>
       <c r="C19" t="n">
-        <v>1018</v>
+        <v>231</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>3330</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="C20" t="n">
-        <v>1019</v>
+        <v>331</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>3430</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>430</v>
       </c>
       <c r="C21" t="n">
-        <v>1020</v>
+        <v>431</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>3040</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C22" t="n">
-        <v>1021</v>
+        <v>41</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>3140</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>140</v>
       </c>
       <c r="C23" t="n">
-        <v>1022</v>
+        <v>141</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>3240</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>240</v>
       </c>
       <c r="C24" t="n">
-        <v>1023</v>
+        <v>241</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>3340</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>340</v>
       </c>
       <c r="C25" t="n">
-        <v>1024</v>
+        <v>341</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>3440</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>440</v>
       </c>
       <c r="C26" t="n">
-        <v>1025</v>
+        <v>441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1001</v>
+        <v>3001</v>
       </c>
       <c r="B27" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>2001</v>
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1002</v>
+        <v>3101</v>
       </c>
       <c r="B28" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="C28" t="n">
-        <v>2002</v>
+        <v>102</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1003</v>
+        <v>3201</v>
       </c>
       <c r="B29" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="C29" t="n">
-        <v>2003</v>
+        <v>202</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1004</v>
+        <v>3301</v>
       </c>
       <c r="B30" t="n">
-        <v>1004</v>
+        <v>301</v>
       </c>
       <c r="C30" t="n">
-        <v>2004</v>
+        <v>302</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1005</v>
+        <v>3401</v>
       </c>
       <c r="B31" t="n">
-        <v>1005</v>
+        <v>401</v>
       </c>
       <c r="C31" t="n">
-        <v>2005</v>
+        <v>402</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1006</v>
+        <v>3011</v>
       </c>
       <c r="B32" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>2006</v>
+        <v>12</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1007</v>
+        <v>3111</v>
       </c>
       <c r="B33" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="C33" t="n">
-        <v>2007</v>
+        <v>112</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1008</v>
+        <v>3211</v>
       </c>
       <c r="B34" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="C34" t="n">
-        <v>2008</v>
+        <v>212</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1009</v>
+        <v>3311</v>
       </c>
       <c r="B35" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="C35" t="n">
-        <v>2009</v>
+        <v>312</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1010</v>
+        <v>3411</v>
       </c>
       <c r="B36" t="n">
-        <v>1010</v>
+        <v>411</v>
       </c>
       <c r="C36" t="n">
-        <v>2010</v>
+        <v>412</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1011</v>
+        <v>3021</v>
       </c>
       <c r="B37" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="C37" t="n">
-        <v>2011</v>
+        <v>22</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1012</v>
+        <v>3121</v>
       </c>
       <c r="B38" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="C38" t="n">
-        <v>2012</v>
+        <v>122</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1013</v>
+        <v>3221</v>
       </c>
       <c r="B39" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="C39" t="n">
-        <v>2013</v>
+        <v>222</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1014</v>
+        <v>3321</v>
       </c>
       <c r="B40" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="C40" t="n">
-        <v>2014</v>
+        <v>322</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1015</v>
+        <v>3421</v>
       </c>
       <c r="B41" t="n">
-        <v>1015</v>
+        <v>421</v>
       </c>
       <c r="C41" t="n">
-        <v>2015</v>
+        <v>422</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1016</v>
+        <v>3031</v>
       </c>
       <c r="B42" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="C42" t="n">
-        <v>2016</v>
+        <v>32</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1017</v>
+        <v>3131</v>
       </c>
       <c r="B43" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="C43" t="n">
-        <v>2017</v>
+        <v>132</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1018</v>
+        <v>3231</v>
       </c>
       <c r="B44" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="C44" t="n">
-        <v>2018</v>
+        <v>232</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1019</v>
+        <v>3331</v>
       </c>
       <c r="B45" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="C45" t="n">
-        <v>2019</v>
+        <v>332</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1020</v>
+        <v>3431</v>
       </c>
       <c r="B46" t="n">
-        <v>1020</v>
+        <v>431</v>
       </c>
       <c r="C46" t="n">
-        <v>2020</v>
+        <v>432</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1021</v>
+        <v>3041</v>
       </c>
       <c r="B47" t="n">
-        <v>1021</v>
+        <v>41</v>
       </c>
       <c r="C47" t="n">
-        <v>2021</v>
+        <v>42</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1022</v>
+        <v>3141</v>
       </c>
       <c r="B48" t="n">
-        <v>1022</v>
+        <v>141</v>
       </c>
       <c r="C48" t="n">
-        <v>2022</v>
+        <v>142</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1023</v>
+        <v>3241</v>
       </c>
       <c r="B49" t="n">
-        <v>1023</v>
+        <v>241</v>
       </c>
       <c r="C49" t="n">
-        <v>2023</v>
+        <v>242</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1024</v>
+        <v>3341</v>
       </c>
       <c r="B50" t="n">
-        <v>1024</v>
+        <v>341</v>
       </c>
       <c r="C50" t="n">
-        <v>2024</v>
+        <v>342</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1025</v>
+        <v>3441</v>
       </c>
       <c r="B51" t="n">
-        <v>1025</v>
+        <v>441</v>
       </c>
       <c r="C51" t="n">
-        <v>2025</v>
+        <v>442</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2001</v>
+        <v>3002</v>
       </c>
       <c r="B52" t="n">
-        <v>2001</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
-        <v>3001</v>
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2002</v>
+        <v>3102</v>
       </c>
       <c r="B53" t="n">
-        <v>2002</v>
+        <v>102</v>
       </c>
       <c r="C53" t="n">
-        <v>3002</v>
+        <v>103</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2003</v>
+        <v>3202</v>
       </c>
       <c r="B54" t="n">
-        <v>2003</v>
+        <v>202</v>
       </c>
       <c r="C54" t="n">
-        <v>3003</v>
+        <v>203</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2004</v>
+        <v>3302</v>
       </c>
       <c r="B55" t="n">
-        <v>2004</v>
+        <v>302</v>
       </c>
       <c r="C55" t="n">
-        <v>3004</v>
+        <v>303</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2005</v>
+        <v>3402</v>
       </c>
       <c r="B56" t="n">
-        <v>2005</v>
+        <v>402</v>
       </c>
       <c r="C56" t="n">
-        <v>3005</v>
+        <v>403</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2006</v>
+        <v>3012</v>
       </c>
       <c r="B57" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="C57" t="n">
-        <v>3006</v>
+        <v>13</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2007</v>
+        <v>3112</v>
       </c>
       <c r="B58" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="C58" t="n">
-        <v>3007</v>
+        <v>113</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2008</v>
+        <v>3212</v>
       </c>
       <c r="B59" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="C59" t="n">
-        <v>3008</v>
+        <v>213</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2009</v>
+        <v>3312</v>
       </c>
       <c r="B60" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="C60" t="n">
-        <v>3009</v>
+        <v>313</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2010</v>
+        <v>3412</v>
       </c>
       <c r="B61" t="n">
-        <v>2010</v>
+        <v>412</v>
       </c>
       <c r="C61" t="n">
-        <v>3010</v>
+        <v>413</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2011</v>
+        <v>3022</v>
       </c>
       <c r="B62" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="C62" t="n">
-        <v>3011</v>
+        <v>23</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2012</v>
+        <v>3122</v>
       </c>
       <c r="B63" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="C63" t="n">
-        <v>3012</v>
+        <v>123</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2013</v>
+        <v>3222</v>
       </c>
       <c r="B64" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="C64" t="n">
-        <v>3013</v>
+        <v>223</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2014</v>
+        <v>3322</v>
       </c>
       <c r="B65" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="C65" t="n">
-        <v>3014</v>
+        <v>323</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2015</v>
+        <v>3422</v>
       </c>
       <c r="B66" t="n">
-        <v>2015</v>
+        <v>422</v>
       </c>
       <c r="C66" t="n">
-        <v>3015</v>
+        <v>423</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2016</v>
+        <v>3032</v>
       </c>
       <c r="B67" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="C67" t="n">
-        <v>3016</v>
+        <v>33</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2017</v>
+        <v>3132</v>
       </c>
       <c r="B68" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="C68" t="n">
-        <v>3017</v>
+        <v>133</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2018</v>
+        <v>3232</v>
       </c>
       <c r="B69" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="C69" t="n">
-        <v>3018</v>
+        <v>233</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2019</v>
+        <v>3332</v>
       </c>
       <c r="B70" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="C70" t="n">
-        <v>3019</v>
+        <v>333</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2020</v>
+        <v>3432</v>
       </c>
       <c r="B71" t="n">
-        <v>2020</v>
+        <v>432</v>
       </c>
       <c r="C71" t="n">
-        <v>3020</v>
+        <v>433</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2021</v>
+        <v>3042</v>
       </c>
       <c r="B72" t="n">
-        <v>2021</v>
+        <v>42</v>
       </c>
       <c r="C72" t="n">
-        <v>3021</v>
+        <v>43</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022</v>
+        <v>3142</v>
       </c>
       <c r="B73" t="n">
-        <v>2022</v>
+        <v>142</v>
       </c>
       <c r="C73" t="n">
-        <v>3022</v>
+        <v>143</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2023</v>
+        <v>3242</v>
       </c>
       <c r="B74" t="n">
-        <v>2023</v>
+        <v>242</v>
       </c>
       <c r="C74" t="n">
-        <v>3023</v>
+        <v>243</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2024</v>
+        <v>3342</v>
       </c>
       <c r="B75" t="n">
-        <v>2024</v>
+        <v>342</v>
       </c>
       <c r="C75" t="n">
-        <v>3024</v>
+        <v>343</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2025</v>
+        <v>3442</v>
       </c>
       <c r="B76" t="n">
-        <v>2025</v>
+        <v>442</v>
       </c>
       <c r="C76" t="n">
-        <v>3025</v>
+        <v>443</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3001</v>
+        <v>3003</v>
       </c>
       <c r="B77" t="n">
-        <v>3001</v>
+        <v>3</v>
       </c>
       <c r="C77" t="n">
-        <v>4001</v>
+        <v>4</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3002</v>
+        <v>3103</v>
       </c>
       <c r="B78" t="n">
-        <v>3002</v>
+        <v>103</v>
       </c>
       <c r="C78" t="n">
-        <v>4002</v>
+        <v>104</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3003</v>
+        <v>3203</v>
       </c>
       <c r="B79" t="n">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="C79" t="n">
-        <v>4003</v>
+        <v>204</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3004</v>
+        <v>3303</v>
       </c>
       <c r="B80" t="n">
-        <v>3004</v>
+        <v>303</v>
       </c>
       <c r="C80" t="n">
-        <v>4004</v>
+        <v>304</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3005</v>
+        <v>3403</v>
       </c>
       <c r="B81" t="n">
-        <v>3005</v>
+        <v>403</v>
       </c>
       <c r="C81" t="n">
-        <v>4005</v>
+        <v>404</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3006</v>
+        <v>3013</v>
       </c>
       <c r="B82" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="C82" t="n">
-        <v>4006</v>
+        <v>14</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3007</v>
+        <v>3113</v>
       </c>
       <c r="B83" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="C83" t="n">
-        <v>4007</v>
+        <v>114</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3008</v>
+        <v>3213</v>
       </c>
       <c r="B84" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="C84" t="n">
-        <v>4008</v>
+        <v>214</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>3009</v>
+        <v>3313</v>
       </c>
       <c r="B85" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="C85" t="n">
-        <v>4009</v>
+        <v>314</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>3010</v>
+        <v>3413</v>
       </c>
       <c r="B86" t="n">
-        <v>3010</v>
+        <v>413</v>
       </c>
       <c r="C86" t="n">
-        <v>4010</v>
+        <v>414</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>3011</v>
+        <v>3023</v>
       </c>
       <c r="B87" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="C87" t="n">
-        <v>4011</v>
+        <v>24</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>3012</v>
+        <v>3123</v>
       </c>
       <c r="B88" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="C88" t="n">
-        <v>4012</v>
+        <v>124</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>3013</v>
+        <v>3223</v>
       </c>
       <c r="B89" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="C89" t="n">
-        <v>4013</v>
+        <v>224</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>3014</v>
+        <v>3323</v>
       </c>
       <c r="B90" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="C90" t="n">
-        <v>4014</v>
+        <v>324</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3015</v>
+        <v>3423</v>
       </c>
       <c r="B91" t="n">
-        <v>3015</v>
+        <v>423</v>
       </c>
       <c r="C91" t="n">
-        <v>4015</v>
+        <v>424</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3016</v>
+        <v>3033</v>
       </c>
       <c r="B92" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="C92" t="n">
-        <v>4016</v>
+        <v>34</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>3017</v>
+        <v>3133</v>
       </c>
       <c r="B93" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="C93" t="n">
-        <v>4017</v>
+        <v>134</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>3018</v>
+        <v>3233</v>
       </c>
       <c r="B94" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="C94" t="n">
-        <v>4018</v>
+        <v>234</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>3019</v>
+        <v>3333</v>
       </c>
       <c r="B95" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="C95" t="n">
-        <v>4019</v>
+        <v>334</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>3020</v>
+        <v>3433</v>
       </c>
       <c r="B96" t="n">
-        <v>3020</v>
+        <v>433</v>
       </c>
       <c r="C96" t="n">
-        <v>4020</v>
+        <v>434</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>3021</v>
+        <v>3043</v>
       </c>
       <c r="B97" t="n">
-        <v>3021</v>
+        <v>43</v>
       </c>
       <c r="C97" t="n">
-        <v>4021</v>
+        <v>44</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>3022</v>
+        <v>3143</v>
       </c>
       <c r="B98" t="n">
-        <v>3022</v>
+        <v>143</v>
       </c>
       <c r="C98" t="n">
-        <v>4022</v>
+        <v>144</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3023</v>
+        <v>3243</v>
       </c>
       <c r="B99" t="n">
-        <v>3023</v>
+        <v>243</v>
       </c>
       <c r="C99" t="n">
-        <v>4023</v>
+        <v>244</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3024</v>
+        <v>3343</v>
       </c>
       <c r="B100" t="n">
-        <v>3024</v>
+        <v>343</v>
       </c>
       <c r="C100" t="n">
-        <v>4024</v>
+        <v>344</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3025</v>
+        <v>3443</v>
       </c>
       <c r="B101" t="n">
-        <v>3025</v>
+        <v>443</v>
       </c>
       <c r="C101" t="n">
-        <v>4025</v>
+        <v>444</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>1026</v>
+        <v>1001</v>
       </c>
       <c r="B102" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>1002</v>
+        <v>101</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>1027</v>
+        <v>1101</v>
       </c>
       <c r="B103" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="C103" t="n">
-        <v>1003</v>
+        <v>201</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>1028</v>
+        <v>1201</v>
       </c>
       <c r="B104" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="C104" t="n">
-        <v>1004</v>
+        <v>301</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1029</v>
+        <v>1301</v>
       </c>
       <c r="B105" t="n">
-        <v>1004</v>
+        <v>301</v>
       </c>
       <c r="C105" t="n">
-        <v>1005</v>
+        <v>401</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="B106" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="C106" t="n">
-        <v>1007</v>
+        <v>111</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>1031</v>
+        <v>1111</v>
       </c>
       <c r="B107" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="C107" t="n">
-        <v>1008</v>
+        <v>211</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>1032</v>
+        <v>1211</v>
       </c>
       <c r="B108" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="C108" t="n">
-        <v>1009</v>
+        <v>311</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>1033</v>
+        <v>1311</v>
       </c>
       <c r="B109" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="C109" t="n">
-        <v>1010</v>
+        <v>411</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="B110" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="C110" t="n">
-        <v>1012</v>
+        <v>121</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>1035</v>
+        <v>1121</v>
       </c>
       <c r="B111" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="C111" t="n">
-        <v>1013</v>
+        <v>221</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>1036</v>
+        <v>1221</v>
       </c>
       <c r="B112" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="C112" t="n">
-        <v>1014</v>
+        <v>321</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>1037</v>
+        <v>1321</v>
       </c>
       <c r="B113" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="C113" t="n">
-        <v>1015</v>
+        <v>421</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="B114" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="C114" t="n">
-        <v>1017</v>
+        <v>131</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>1039</v>
+        <v>1131</v>
       </c>
       <c r="B115" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="C115" t="n">
-        <v>1018</v>
+        <v>231</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>1040</v>
+        <v>1231</v>
       </c>
       <c r="B116" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="C116" t="n">
-        <v>1019</v>
+        <v>331</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1041</v>
+        <v>1331</v>
       </c>
       <c r="B117" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="C117" t="n">
-        <v>1020</v>
+        <v>431</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B118" t="n">
-        <v>1021</v>
+        <v>41</v>
       </c>
       <c r="C118" t="n">
-        <v>1022</v>
+        <v>141</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>1043</v>
+        <v>1141</v>
       </c>
       <c r="B119" t="n">
-        <v>1022</v>
+        <v>141</v>
       </c>
       <c r="C119" t="n">
-        <v>1023</v>
+        <v>241</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1044</v>
+        <v>1241</v>
       </c>
       <c r="B120" t="n">
-        <v>1023</v>
+        <v>241</v>
       </c>
       <c r="C120" t="n">
-        <v>1024</v>
+        <v>341</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1045</v>
+        <v>1341</v>
       </c>
       <c r="B121" t="n">
-        <v>1024</v>
+        <v>341</v>
       </c>
       <c r="C121" t="n">
-        <v>1025</v>
+        <v>441</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2026</v>
+        <v>1002</v>
       </c>
       <c r="B122" t="n">
-        <v>2001</v>
+        <v>2</v>
       </c>
       <c r="C122" t="n">
-        <v>2002</v>
+        <v>102</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2027</v>
+        <v>1102</v>
       </c>
       <c r="B123" t="n">
-        <v>2002</v>
+        <v>102</v>
       </c>
       <c r="C123" t="n">
-        <v>2003</v>
+        <v>202</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2028</v>
+        <v>1202</v>
       </c>
       <c r="B124" t="n">
-        <v>2003</v>
+        <v>202</v>
       </c>
       <c r="C124" t="n">
-        <v>2004</v>
+        <v>302</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2029</v>
+        <v>1302</v>
       </c>
       <c r="B125" t="n">
-        <v>2004</v>
+        <v>302</v>
       </c>
       <c r="C125" t="n">
-        <v>2005</v>
+        <v>402</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2030</v>
+        <v>1012</v>
       </c>
       <c r="B126" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="C126" t="n">
-        <v>2007</v>
+        <v>112</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2031</v>
+        <v>1112</v>
       </c>
       <c r="B127" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="C127" t="n">
-        <v>2008</v>
+        <v>212</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2032</v>
+        <v>1212</v>
       </c>
       <c r="B128" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="C128" t="n">
-        <v>2009</v>
+        <v>312</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2033</v>
+        <v>1312</v>
       </c>
       <c r="B129" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="C129" t="n">
-        <v>2010</v>
+        <v>412</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2034</v>
+        <v>1022</v>
       </c>
       <c r="B130" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="C130" t="n">
-        <v>2012</v>
+        <v>122</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2035</v>
+        <v>1122</v>
       </c>
       <c r="B131" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="C131" t="n">
-        <v>2013</v>
+        <v>222</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2036</v>
+        <v>1222</v>
       </c>
       <c r="B132" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="C132" t="n">
-        <v>2014</v>
+        <v>322</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2037</v>
+        <v>1322</v>
       </c>
       <c r="B133" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="C133" t="n">
-        <v>2015</v>
+        <v>422</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2038</v>
+        <v>1032</v>
       </c>
       <c r="B134" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="C134" t="n">
-        <v>2017</v>
+        <v>132</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2039</v>
+        <v>1132</v>
       </c>
       <c r="B135" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="C135" t="n">
-        <v>2018</v>
+        <v>232</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2040</v>
+        <v>1232</v>
       </c>
       <c r="B136" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="C136" t="n">
-        <v>2019</v>
+        <v>332</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2041</v>
+        <v>1332</v>
       </c>
       <c r="B137" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="C137" t="n">
-        <v>2020</v>
+        <v>432</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2042</v>
+        <v>1042</v>
       </c>
       <c r="B138" t="n">
-        <v>2021</v>
+        <v>42</v>
       </c>
       <c r="C138" t="n">
-        <v>2022</v>
+        <v>142</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2043</v>
+        <v>1142</v>
       </c>
       <c r="B139" t="n">
-        <v>2022</v>
+        <v>142</v>
       </c>
       <c r="C139" t="n">
-        <v>2023</v>
+        <v>242</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2044</v>
+        <v>1242</v>
       </c>
       <c r="B140" t="n">
-        <v>2023</v>
+        <v>242</v>
       </c>
       <c r="C140" t="n">
-        <v>2024</v>
+        <v>342</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2045</v>
+        <v>1342</v>
       </c>
       <c r="B141" t="n">
-        <v>2024</v>
+        <v>342</v>
       </c>
       <c r="C141" t="n">
-        <v>2025</v>
+        <v>442</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>3026</v>
+        <v>1003</v>
       </c>
       <c r="B142" t="n">
-        <v>3001</v>
+        <v>3</v>
       </c>
       <c r="C142" t="n">
-        <v>3002</v>
+        <v>103</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>3027</v>
+        <v>1103</v>
       </c>
       <c r="B143" t="n">
-        <v>3002</v>
+        <v>103</v>
       </c>
       <c r="C143" t="n">
-        <v>3003</v>
+        <v>203</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>3028</v>
+        <v>1203</v>
       </c>
       <c r="B144" t="n">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="C144" t="n">
-        <v>3004</v>
+        <v>303</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>3029</v>
+        <v>1303</v>
       </c>
       <c r="B145" t="n">
-        <v>3004</v>
+        <v>303</v>
       </c>
       <c r="C145" t="n">
-        <v>3005</v>
+        <v>403</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>3030</v>
+        <v>1013</v>
       </c>
       <c r="B146" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="C146" t="n">
-        <v>3007</v>
+        <v>113</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>3031</v>
+        <v>1113</v>
       </c>
       <c r="B147" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="C147" t="n">
-        <v>3008</v>
+        <v>213</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>3032</v>
+        <v>1213</v>
       </c>
       <c r="B148" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="C148" t="n">
-        <v>3009</v>
+        <v>313</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>3033</v>
+        <v>1313</v>
       </c>
       <c r="B149" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="C149" t="n">
-        <v>3010</v>
+        <v>413</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>3034</v>
+        <v>1023</v>
       </c>
       <c r="B150" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="C150" t="n">
-        <v>3012</v>
+        <v>123</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>3035</v>
+        <v>1123</v>
       </c>
       <c r="B151" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="C151" t="n">
-        <v>3013</v>
+        <v>223</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>3036</v>
+        <v>1223</v>
       </c>
       <c r="B152" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="C152" t="n">
-        <v>3014</v>
+        <v>323</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>3037</v>
+        <v>1323</v>
       </c>
       <c r="B153" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="C153" t="n">
-        <v>3015</v>
+        <v>423</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3038</v>
+        <v>1033</v>
       </c>
       <c r="B154" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="C154" t="n">
-        <v>3017</v>
+        <v>133</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>3039</v>
+        <v>1133</v>
       </c>
       <c r="B155" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="C155" t="n">
-        <v>3018</v>
+        <v>233</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>3040</v>
+        <v>1233</v>
       </c>
       <c r="B156" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="C156" t="n">
-        <v>3019</v>
+        <v>333</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>3041</v>
+        <v>1333</v>
       </c>
       <c r="B157" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="C157" t="n">
-        <v>3020</v>
+        <v>433</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>3042</v>
+        <v>1043</v>
       </c>
       <c r="B158" t="n">
-        <v>3021</v>
+        <v>43</v>
       </c>
       <c r="C158" t="n">
-        <v>3022</v>
+        <v>143</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3043</v>
+        <v>1143</v>
       </c>
       <c r="B159" t="n">
-        <v>3022</v>
+        <v>143</v>
       </c>
       <c r="C159" t="n">
-        <v>3023</v>
+        <v>243</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>3044</v>
+        <v>1243</v>
       </c>
       <c r="B160" t="n">
-        <v>3023</v>
+        <v>243</v>
       </c>
       <c r="C160" t="n">
-        <v>3024</v>
+        <v>343</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>3045</v>
+        <v>1343</v>
       </c>
       <c r="B161" t="n">
-        <v>3024</v>
+        <v>343</v>
       </c>
       <c r="C161" t="n">
-        <v>3025</v>
+        <v>443</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>4026</v>
+        <v>1004</v>
       </c>
       <c r="B162" t="n">
-        <v>4001</v>
+        <v>4</v>
       </c>
       <c r="C162" t="n">
-        <v>4002</v>
+        <v>104</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>4027</v>
+        <v>1104</v>
       </c>
       <c r="B163" t="n">
-        <v>4002</v>
+        <v>104</v>
       </c>
       <c r="C163" t="n">
-        <v>4003</v>
+        <v>204</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>4028</v>
+        <v>1204</v>
       </c>
       <c r="B164" t="n">
-        <v>4003</v>
+        <v>204</v>
       </c>
       <c r="C164" t="n">
-        <v>4004</v>
+        <v>304</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>4029</v>
+        <v>1304</v>
       </c>
       <c r="B165" t="n">
-        <v>4004</v>
+        <v>304</v>
       </c>
       <c r="C165" t="n">
-        <v>4005</v>
+        <v>404</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>4030</v>
+        <v>1014</v>
       </c>
       <c r="B166" t="n">
-        <v>4006</v>
+        <v>14</v>
       </c>
       <c r="C166" t="n">
-        <v>4007</v>
+        <v>114</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>4031</v>
+        <v>1114</v>
       </c>
       <c r="B167" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="C167" t="n">
-        <v>4008</v>
+        <v>214</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>4032</v>
+        <v>1214</v>
       </c>
       <c r="B168" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="C168" t="n">
-        <v>4009</v>
+        <v>314</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>4033</v>
+        <v>1314</v>
       </c>
       <c r="B169" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="C169" t="n">
-        <v>4010</v>
+        <v>414</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>4034</v>
+        <v>1024</v>
       </c>
       <c r="B170" t="n">
-        <v>4011</v>
+        <v>24</v>
       </c>
       <c r="C170" t="n">
-        <v>4012</v>
+        <v>124</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>4035</v>
+        <v>1124</v>
       </c>
       <c r="B171" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="C171" t="n">
-        <v>4013</v>
+        <v>224</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>4036</v>
+        <v>1224</v>
       </c>
       <c r="B172" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="C172" t="n">
-        <v>4014</v>
+        <v>324</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>4037</v>
+        <v>1324</v>
       </c>
       <c r="B173" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="C173" t="n">
-        <v>4015</v>
+        <v>424</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>4038</v>
+        <v>1034</v>
       </c>
       <c r="B174" t="n">
-        <v>4016</v>
+        <v>34</v>
       </c>
       <c r="C174" t="n">
-        <v>4017</v>
+        <v>134</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>4039</v>
+        <v>1134</v>
       </c>
       <c r="B175" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="C175" t="n">
-        <v>4018</v>
+        <v>234</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>4040</v>
+        <v>1234</v>
       </c>
       <c r="B176" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="C176" t="n">
-        <v>4019</v>
+        <v>334</v>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>4041</v>
+        <v>1334</v>
       </c>
       <c r="B177" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="C177" t="n">
-        <v>4020</v>
+        <v>434</v>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>4042</v>
+        <v>1044</v>
       </c>
       <c r="B178" t="n">
-        <v>4021</v>
+        <v>44</v>
       </c>
       <c r="C178" t="n">
-        <v>4022</v>
+        <v>144</v>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>4043</v>
+        <v>1144</v>
       </c>
       <c r="B179" t="n">
-        <v>4022</v>
+        <v>144</v>
       </c>
       <c r="C179" t="n">
-        <v>4023</v>
+        <v>244</v>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>4044</v>
+        <v>1244</v>
       </c>
       <c r="B180" t="n">
-        <v>4023</v>
+        <v>244</v>
       </c>
       <c r="C180" t="n">
-        <v>4024</v>
+        <v>344</v>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>4045</v>
+        <v>1344</v>
       </c>
       <c r="B181" t="n">
-        <v>4024</v>
+        <v>344</v>
       </c>
       <c r="C181" t="n">
-        <v>4025</v>
+        <v>444</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>1046</v>
+        <v>2001</v>
       </c>
       <c r="B182" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>1006</v>
+        <v>11</v>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1047</v>
+        <v>2101</v>
       </c>
       <c r="B183" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="C183" t="n">
-        <v>1007</v>
+        <v>111</v>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1048</v>
+        <v>2201</v>
       </c>
       <c r="B184" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="C184" t="n">
-        <v>1008</v>
+        <v>211</v>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>1049</v>
+        <v>2301</v>
       </c>
       <c r="B185" t="n">
-        <v>1004</v>
+        <v>301</v>
       </c>
       <c r="C185" t="n">
-        <v>1009</v>
+        <v>311</v>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>1050</v>
+        <v>2401</v>
       </c>
       <c r="B186" t="n">
-        <v>1005</v>
+        <v>401</v>
       </c>
       <c r="C186" t="n">
-        <v>1010</v>
+        <v>411</v>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>1051</v>
+        <v>2011</v>
       </c>
       <c r="B187" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="C187" t="n">
-        <v>1011</v>
+        <v>21</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>1052</v>
+        <v>2111</v>
       </c>
       <c r="B188" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="C188" t="n">
-        <v>1012</v>
+        <v>121</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>1053</v>
+        <v>2211</v>
       </c>
       <c r="B189" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="C189" t="n">
-        <v>1013</v>
+        <v>221</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>1054</v>
+        <v>2311</v>
       </c>
       <c r="B190" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="C190" t="n">
-        <v>1014</v>
+        <v>321</v>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>1055</v>
+        <v>2411</v>
       </c>
       <c r="B191" t="n">
-        <v>1010</v>
+        <v>411</v>
       </c>
       <c r="C191" t="n">
-        <v>1015</v>
+        <v>421</v>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>1056</v>
+        <v>2021</v>
       </c>
       <c r="B192" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="C192" t="n">
-        <v>1016</v>
+        <v>31</v>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>1057</v>
+        <v>2121</v>
       </c>
       <c r="B193" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="C193" t="n">
-        <v>1017</v>
+        <v>131</v>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>1058</v>
+        <v>2221</v>
       </c>
       <c r="B194" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="C194" t="n">
-        <v>1018</v>
+        <v>231</v>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>1059</v>
+        <v>2321</v>
       </c>
       <c r="B195" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="C195" t="n">
-        <v>1019</v>
+        <v>331</v>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>1060</v>
+        <v>2421</v>
       </c>
       <c r="B196" t="n">
-        <v>1015</v>
+        <v>421</v>
       </c>
       <c r="C196" t="n">
-        <v>1020</v>
+        <v>431</v>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>1061</v>
+        <v>2031</v>
       </c>
       <c r="B197" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="C197" t="n">
-        <v>1021</v>
+        <v>41</v>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>1062</v>
+        <v>2131</v>
       </c>
       <c r="B198" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="C198" t="n">
-        <v>1022</v>
+        <v>141</v>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>1063</v>
+        <v>2231</v>
       </c>
       <c r="B199" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="C199" t="n">
-        <v>1023</v>
+        <v>241</v>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>1064</v>
+        <v>2331</v>
       </c>
       <c r="B200" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="C200" t="n">
-        <v>1024</v>
+        <v>341</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>1065</v>
+        <v>2431</v>
       </c>
       <c r="B201" t="n">
-        <v>1020</v>
+        <v>431</v>
       </c>
       <c r="C201" t="n">
-        <v>1025</v>
+        <v>441</v>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>2046</v>
+        <v>2002</v>
       </c>
       <c r="B202" t="n">
-        <v>2001</v>
+        <v>2</v>
       </c>
       <c r="C202" t="n">
-        <v>2006</v>
+        <v>12</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>2047</v>
+        <v>2102</v>
       </c>
       <c r="B203" t="n">
-        <v>2002</v>
+        <v>102</v>
       </c>
       <c r="C203" t="n">
-        <v>2007</v>
+        <v>112</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>2048</v>
+        <v>2202</v>
       </c>
       <c r="B204" t="n">
-        <v>2003</v>
+        <v>202</v>
       </c>
       <c r="C204" t="n">
-        <v>2008</v>
+        <v>212</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>2049</v>
+        <v>2302</v>
       </c>
       <c r="B205" t="n">
-        <v>2004</v>
+        <v>302</v>
       </c>
       <c r="C205" t="n">
-        <v>2009</v>
+        <v>312</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>2050</v>
+        <v>2402</v>
       </c>
       <c r="B206" t="n">
-        <v>2005</v>
+        <v>402</v>
       </c>
       <c r="C206" t="n">
-        <v>2010</v>
+        <v>412</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>2051</v>
+        <v>2012</v>
       </c>
       <c r="B207" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="C207" t="n">
-        <v>2011</v>
+        <v>22</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>2052</v>
+        <v>2112</v>
       </c>
       <c r="B208" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="C208" t="n">
-        <v>2012</v>
+        <v>122</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>2053</v>
+        <v>2212</v>
       </c>
       <c r="B209" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="C209" t="n">
-        <v>2013</v>
+        <v>222</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>2054</v>
+        <v>2312</v>
       </c>
       <c r="B210" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="C210" t="n">
-        <v>2014</v>
+        <v>322</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>2055</v>
+        <v>2412</v>
       </c>
       <c r="B211" t="n">
-        <v>2010</v>
+        <v>412</v>
       </c>
       <c r="C211" t="n">
-        <v>2015</v>
+        <v>422</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>2056</v>
+        <v>2022</v>
       </c>
       <c r="B212" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="C212" t="n">
-        <v>2016</v>
+        <v>32</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>2057</v>
+        <v>2122</v>
       </c>
       <c r="B213" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="C213" t="n">
-        <v>2017</v>
+        <v>132</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>2058</v>
+        <v>2222</v>
       </c>
       <c r="B214" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="C214" t="n">
-        <v>2018</v>
+        <v>232</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>2059</v>
+        <v>2322</v>
       </c>
       <c r="B215" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="C215" t="n">
-        <v>2019</v>
+        <v>332</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>2060</v>
+        <v>2422</v>
       </c>
       <c r="B216" t="n">
-        <v>2015</v>
+        <v>422</v>
       </c>
       <c r="C216" t="n">
-        <v>2020</v>
+        <v>432</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>2061</v>
+        <v>2032</v>
       </c>
       <c r="B217" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="C217" t="n">
-        <v>2021</v>
+        <v>42</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>2062</v>
+        <v>2132</v>
       </c>
       <c r="B218" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="C218" t="n">
-        <v>2022</v>
+        <v>142</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>2063</v>
+        <v>2232</v>
       </c>
       <c r="B219" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="C219" t="n">
-        <v>2023</v>
+        <v>242</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>2064</v>
+        <v>2332</v>
       </c>
       <c r="B220" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="C220" t="n">
-        <v>2024</v>
+        <v>342</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>2065</v>
+        <v>2432</v>
       </c>
       <c r="B221" t="n">
-        <v>2020</v>
+        <v>432</v>
       </c>
       <c r="C221" t="n">
-        <v>2025</v>
+        <v>442</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>3046</v>
+        <v>2003</v>
       </c>
       <c r="B222" t="n">
-        <v>3001</v>
+        <v>3</v>
       </c>
       <c r="C222" t="n">
-        <v>3006</v>
+        <v>13</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>3047</v>
+        <v>2103</v>
       </c>
       <c r="B223" t="n">
-        <v>3002</v>
+        <v>103</v>
       </c>
       <c r="C223" t="n">
-        <v>3007</v>
+        <v>113</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>3048</v>
+        <v>2203</v>
       </c>
       <c r="B224" t="n">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="C224" t="n">
-        <v>3008</v>
+        <v>213</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>3049</v>
+        <v>2303</v>
       </c>
       <c r="B225" t="n">
-        <v>3004</v>
+        <v>303</v>
       </c>
       <c r="C225" t="n">
-        <v>3009</v>
+        <v>313</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>3050</v>
+        <v>2403</v>
       </c>
       <c r="B226" t="n">
-        <v>3005</v>
+        <v>403</v>
       </c>
       <c r="C226" t="n">
-        <v>3010</v>
+        <v>413</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>3051</v>
+        <v>2013</v>
       </c>
       <c r="B227" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="C227" t="n">
-        <v>3011</v>
+        <v>23</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>3052</v>
+        <v>2113</v>
       </c>
       <c r="B228" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="C228" t="n">
-        <v>3012</v>
+        <v>123</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>3053</v>
+        <v>2213</v>
       </c>
       <c r="B229" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="C229" t="n">
-        <v>3013</v>
+        <v>223</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>3054</v>
+        <v>2313</v>
       </c>
       <c r="B230" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="C230" t="n">
-        <v>3014</v>
+        <v>323</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>3055</v>
+        <v>2413</v>
       </c>
       <c r="B231" t="n">
-        <v>3010</v>
+        <v>413</v>
       </c>
       <c r="C231" t="n">
-        <v>3015</v>
+        <v>423</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>3056</v>
+        <v>2023</v>
       </c>
       <c r="B232" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="C232" t="n">
-        <v>3016</v>
+        <v>33</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>3057</v>
+        <v>2123</v>
       </c>
       <c r="B233" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="C233" t="n">
-        <v>3017</v>
+        <v>133</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>3058</v>
+        <v>2223</v>
       </c>
       <c r="B234" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="C234" t="n">
-        <v>3018</v>
+        <v>233</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>3059</v>
+        <v>2323</v>
       </c>
       <c r="B235" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="C235" t="n">
-        <v>3019</v>
+        <v>333</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>3060</v>
+        <v>2423</v>
       </c>
       <c r="B236" t="n">
-        <v>3015</v>
+        <v>423</v>
       </c>
       <c r="C236" t="n">
-        <v>3020</v>
+        <v>433</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>3061</v>
+        <v>2033</v>
       </c>
       <c r="B237" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="C237" t="n">
-        <v>3021</v>
+        <v>43</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>3062</v>
+        <v>2133</v>
       </c>
       <c r="B238" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="C238" t="n">
-        <v>3022</v>
+        <v>143</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>3063</v>
+        <v>2233</v>
       </c>
       <c r="B239" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="C239" t="n">
-        <v>3023</v>
+        <v>243</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>3064</v>
+        <v>2333</v>
       </c>
       <c r="B240" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="C240" t="n">
-        <v>3024</v>
+        <v>343</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>3065</v>
+        <v>2433</v>
       </c>
       <c r="B241" t="n">
-        <v>3020</v>
+        <v>433</v>
       </c>
       <c r="C241" t="n">
-        <v>3025</v>
+        <v>443</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>4046</v>
+        <v>2004</v>
       </c>
       <c r="B242" t="n">
-        <v>4001</v>
+        <v>4</v>
       </c>
       <c r="C242" t="n">
-        <v>4006</v>
+        <v>14</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>4047</v>
+        <v>2104</v>
       </c>
       <c r="B243" t="n">
-        <v>4002</v>
+        <v>104</v>
       </c>
       <c r="C243" t="n">
-        <v>4007</v>
+        <v>114</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>4048</v>
+        <v>2204</v>
       </c>
       <c r="B244" t="n">
-        <v>4003</v>
+        <v>204</v>
       </c>
       <c r="C244" t="n">
-        <v>4008</v>
+        <v>214</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>4049</v>
+        <v>2304</v>
       </c>
       <c r="B245" t="n">
-        <v>4004</v>
+        <v>304</v>
       </c>
       <c r="C245" t="n">
-        <v>4009</v>
+        <v>314</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>4050</v>
+        <v>2404</v>
       </c>
       <c r="B246" t="n">
-        <v>4005</v>
+        <v>404</v>
       </c>
       <c r="C246" t="n">
-        <v>4010</v>
+        <v>414</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>4051</v>
+        <v>2014</v>
       </c>
       <c r="B247" t="n">
-        <v>4006</v>
+        <v>14</v>
       </c>
       <c r="C247" t="n">
-        <v>4011</v>
+        <v>24</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>4052</v>
+        <v>2114</v>
       </c>
       <c r="B248" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="C248" t="n">
-        <v>4012</v>
+        <v>124</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>4053</v>
+        <v>2214</v>
       </c>
       <c r="B249" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="C249" t="n">
-        <v>4013</v>
+        <v>224</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>4054</v>
+        <v>2314</v>
       </c>
       <c r="B250" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="C250" t="n">
-        <v>4014</v>
+        <v>324</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>4055</v>
+        <v>2414</v>
       </c>
       <c r="B251" t="n">
-        <v>4010</v>
+        <v>414</v>
       </c>
       <c r="C251" t="n">
-        <v>4015</v>
+        <v>424</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>4056</v>
+        <v>2024</v>
       </c>
       <c r="B252" t="n">
-        <v>4011</v>
+        <v>24</v>
       </c>
       <c r="C252" t="n">
-        <v>4016</v>
+        <v>34</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>4057</v>
+        <v>2124</v>
       </c>
       <c r="B253" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="C253" t="n">
-        <v>4017</v>
+        <v>134</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>4058</v>
+        <v>2224</v>
       </c>
       <c r="B254" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="C254" t="n">
-        <v>4018</v>
+        <v>234</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>4059</v>
+        <v>2324</v>
       </c>
       <c r="B255" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="C255" t="n">
-        <v>4019</v>
+        <v>334</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>4060</v>
+        <v>2424</v>
       </c>
       <c r="B256" t="n">
-        <v>4015</v>
+        <v>424</v>
       </c>
       <c r="C256" t="n">
-        <v>4020</v>
+        <v>434</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>4061</v>
+        <v>2034</v>
       </c>
       <c r="B257" t="n">
-        <v>4016</v>
+        <v>34</v>
       </c>
       <c r="C257" t="n">
-        <v>4021</v>
+        <v>44</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>4062</v>
+        <v>2134</v>
       </c>
       <c r="B258" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="C258" t="n">
-        <v>4022</v>
+        <v>144</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>4063</v>
+        <v>2234</v>
       </c>
       <c r="B259" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="C259" t="n">
-        <v>4023</v>
+        <v>244</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>4064</v>
+        <v>2334</v>
       </c>
       <c r="B260" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="C260" t="n">
-        <v>4024</v>
+        <v>344</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>4065</v>
+        <v>2434</v>
       </c>
       <c r="B261" t="n">
-        <v>4020</v>
+        <v>434</v>
       </c>
       <c r="C261" t="n">
-        <v>4025</v>
+        <v>444</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Beam</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5105,7 +7194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5134,1135 +7223,1488 @@
           <t>point-4</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>infill-type</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
         <v>1001</v>
       </c>
       <c r="B2" t="n">
-        <v>1001</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="E2" t="n">
-        <v>1002</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Stairs</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1002</v>
+        <v>1101</v>
       </c>
       <c r="B3" t="n">
-        <v>1002</v>
+        <v>101</v>
       </c>
       <c r="C3" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="D3" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="E3" t="n">
-        <v>1003</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1003</v>
+        <v>1201</v>
       </c>
       <c r="B4" t="n">
-        <v>1003</v>
+        <v>201</v>
       </c>
       <c r="C4" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="D4" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="E4" t="n">
-        <v>1004</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1004</v>
+        <v>1301</v>
       </c>
       <c r="B5" t="n">
-        <v>1004</v>
+        <v>301</v>
       </c>
       <c r="C5" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="D5" t="n">
-        <v>1010</v>
+        <v>411</v>
       </c>
       <c r="E5" t="n">
-        <v>1005</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1005</v>
+        <v>1011</v>
       </c>
       <c r="B6" t="n">
-        <v>1006</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="E6" t="n">
-        <v>1007</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1006</v>
+        <v>1111</v>
       </c>
       <c r="B7" t="n">
-        <v>1007</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="D7" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="E7" t="n">
-        <v>1008</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1007</v>
+        <v>1211</v>
       </c>
       <c r="B8" t="n">
-        <v>1008</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="E8" t="n">
-        <v>1009</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1008</v>
+        <v>1311</v>
       </c>
       <c r="B9" t="n">
-        <v>1009</v>
+        <v>311</v>
       </c>
       <c r="C9" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="D9" t="n">
-        <v>1015</v>
+        <v>421</v>
       </c>
       <c r="E9" t="n">
-        <v>1010</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1009</v>
+        <v>1021</v>
       </c>
       <c r="B10" t="n">
-        <v>1011</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="D10" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="E10" t="n">
-        <v>1012</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1010</v>
+        <v>1121</v>
       </c>
       <c r="B11" t="n">
-        <v>1012</v>
+        <v>121</v>
       </c>
       <c r="C11" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="E11" t="n">
-        <v>1013</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1011</v>
+        <v>1221</v>
       </c>
       <c r="B12" t="n">
-        <v>1013</v>
+        <v>221</v>
       </c>
       <c r="C12" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="D12" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="E12" t="n">
-        <v>1014</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1012</v>
+        <v>1321</v>
       </c>
       <c r="B13" t="n">
-        <v>1014</v>
+        <v>321</v>
       </c>
       <c r="C13" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="D13" t="n">
-        <v>1020</v>
+        <v>431</v>
       </c>
       <c r="E13" t="n">
-        <v>1015</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1013</v>
+        <v>1031</v>
       </c>
       <c r="B14" t="n">
-        <v>1016</v>
+        <v>31</v>
       </c>
       <c r="C14" t="n">
-        <v>1021</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>1022</v>
+        <v>141</v>
       </c>
       <c r="E14" t="n">
-        <v>1017</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1014</v>
+        <v>1131</v>
       </c>
       <c r="B15" t="n">
-        <v>1017</v>
+        <v>131</v>
       </c>
       <c r="C15" t="n">
-        <v>1022</v>
+        <v>141</v>
       </c>
       <c r="D15" t="n">
-        <v>1023</v>
+        <v>241</v>
       </c>
       <c r="E15" t="n">
-        <v>1018</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1015</v>
+        <v>1231</v>
       </c>
       <c r="B16" t="n">
-        <v>1018</v>
+        <v>231</v>
       </c>
       <c r="C16" t="n">
-        <v>1023</v>
+        <v>241</v>
       </c>
       <c r="D16" t="n">
-        <v>1024</v>
+        <v>341</v>
       </c>
       <c r="E16" t="n">
-        <v>1019</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1016</v>
+        <v>1331</v>
       </c>
       <c r="B17" t="n">
-        <v>1019</v>
+        <v>331</v>
       </c>
       <c r="C17" t="n">
-        <v>1024</v>
+        <v>341</v>
       </c>
       <c r="D17" t="n">
-        <v>1025</v>
+        <v>441</v>
       </c>
       <c r="E17" t="n">
-        <v>1020</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2001</v>
+        <v>1002</v>
       </c>
       <c r="B18" t="n">
-        <v>2001</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="E18" t="n">
-        <v>2002</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stairs</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2002</v>
+        <v>1102</v>
       </c>
       <c r="B19" t="n">
-        <v>2002</v>
+        <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="D19" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="E19" t="n">
-        <v>2003</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2003</v>
+        <v>1202</v>
       </c>
       <c r="B20" t="n">
-        <v>2003</v>
+        <v>202</v>
       </c>
       <c r="C20" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="D20" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="E20" t="n">
-        <v>2004</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2004</v>
+        <v>1302</v>
       </c>
       <c r="B21" t="n">
-        <v>2004</v>
+        <v>302</v>
       </c>
       <c r="C21" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="D21" t="n">
-        <v>2010</v>
+        <v>412</v>
       </c>
       <c r="E21" t="n">
-        <v>2005</v>
-      </c>
+        <v>402</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2005</v>
+        <v>1012</v>
       </c>
       <c r="B22" t="n">
-        <v>2006</v>
+        <v>12</v>
       </c>
       <c r="C22" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="D22" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="E22" t="n">
-        <v>2007</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2006</v>
+        <v>1112</v>
       </c>
       <c r="B23" t="n">
-        <v>2007</v>
+        <v>112</v>
       </c>
       <c r="C23" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="D23" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="E23" t="n">
-        <v>2008</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2007</v>
+        <v>1212</v>
       </c>
       <c r="B24" t="n">
-        <v>2008</v>
+        <v>212</v>
       </c>
       <c r="C24" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="D24" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="E24" t="n">
-        <v>2009</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2008</v>
+        <v>1312</v>
       </c>
       <c r="B25" t="n">
-        <v>2009</v>
+        <v>312</v>
       </c>
       <c r="C25" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="D25" t="n">
-        <v>2015</v>
+        <v>422</v>
       </c>
       <c r="E25" t="n">
-        <v>2010</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2009</v>
+        <v>1022</v>
       </c>
       <c r="B26" t="n">
-        <v>2011</v>
+        <v>22</v>
       </c>
       <c r="C26" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="D26" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="E26" t="n">
-        <v>2012</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2010</v>
+        <v>1122</v>
       </c>
       <c r="B27" t="n">
-        <v>2012</v>
+        <v>122</v>
       </c>
       <c r="C27" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="D27" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="E27" t="n">
-        <v>2013</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2011</v>
+        <v>1222</v>
       </c>
       <c r="B28" t="n">
-        <v>2013</v>
+        <v>222</v>
       </c>
       <c r="C28" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="D28" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="E28" t="n">
-        <v>2014</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2012</v>
+        <v>1322</v>
       </c>
       <c r="B29" t="n">
-        <v>2014</v>
+        <v>322</v>
       </c>
       <c r="C29" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="D29" t="n">
-        <v>2020</v>
+        <v>432</v>
       </c>
       <c r="E29" t="n">
-        <v>2015</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2013</v>
+        <v>1032</v>
       </c>
       <c r="B30" t="n">
-        <v>2016</v>
+        <v>32</v>
       </c>
       <c r="C30" t="n">
-        <v>2021</v>
+        <v>42</v>
       </c>
       <c r="D30" t="n">
-        <v>2022</v>
+        <v>142</v>
       </c>
       <c r="E30" t="n">
-        <v>2017</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2014</v>
+        <v>1132</v>
       </c>
       <c r="B31" t="n">
-        <v>2017</v>
+        <v>132</v>
       </c>
       <c r="C31" t="n">
-        <v>2022</v>
+        <v>142</v>
       </c>
       <c r="D31" t="n">
-        <v>2023</v>
+        <v>242</v>
       </c>
       <c r="E31" t="n">
-        <v>2018</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2015</v>
+        <v>1232</v>
       </c>
       <c r="B32" t="n">
-        <v>2018</v>
+        <v>232</v>
       </c>
       <c r="C32" t="n">
-        <v>2023</v>
+        <v>242</v>
       </c>
       <c r="D32" t="n">
-        <v>2024</v>
+        <v>342</v>
       </c>
       <c r="E32" t="n">
-        <v>2019</v>
-      </c>
+        <v>332</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2016</v>
+        <v>1332</v>
       </c>
       <c r="B33" t="n">
-        <v>2019</v>
+        <v>332</v>
       </c>
       <c r="C33" t="n">
-        <v>2024</v>
+        <v>342</v>
       </c>
       <c r="D33" t="n">
-        <v>2025</v>
+        <v>442</v>
       </c>
       <c r="E33" t="n">
-        <v>2020</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>3001</v>
+        <v>1003</v>
       </c>
       <c r="B34" t="n">
-        <v>3001</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="D34" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="E34" t="n">
-        <v>3002</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stairs</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3002</v>
+        <v>1103</v>
       </c>
       <c r="B35" t="n">
-        <v>3002</v>
+        <v>103</v>
       </c>
       <c r="C35" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="D35" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="E35" t="n">
-        <v>3003</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3003</v>
+        <v>1203</v>
       </c>
       <c r="B36" t="n">
-        <v>3003</v>
+        <v>203</v>
       </c>
       <c r="C36" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="D36" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="E36" t="n">
-        <v>3004</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3004</v>
+        <v>1303</v>
       </c>
       <c r="B37" t="n">
-        <v>3004</v>
+        <v>303</v>
       </c>
       <c r="C37" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="D37" t="n">
-        <v>3010</v>
+        <v>413</v>
       </c>
       <c r="E37" t="n">
-        <v>3005</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3005</v>
+        <v>1013</v>
       </c>
       <c r="B38" t="n">
-        <v>3006</v>
+        <v>13</v>
       </c>
       <c r="C38" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="D38" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="E38" t="n">
-        <v>3007</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3006</v>
+        <v>1113</v>
       </c>
       <c r="B39" t="n">
-        <v>3007</v>
+        <v>113</v>
       </c>
       <c r="C39" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="D39" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="E39" t="n">
-        <v>3008</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3007</v>
+        <v>1213</v>
       </c>
       <c r="B40" t="n">
-        <v>3008</v>
+        <v>213</v>
       </c>
       <c r="C40" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="D40" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="E40" t="n">
-        <v>3009</v>
-      </c>
+        <v>313</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>3008</v>
+        <v>1313</v>
       </c>
       <c r="B41" t="n">
-        <v>3009</v>
+        <v>313</v>
       </c>
       <c r="C41" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="D41" t="n">
-        <v>3015</v>
+        <v>423</v>
       </c>
       <c r="E41" t="n">
-        <v>3010</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3009</v>
+        <v>1023</v>
       </c>
       <c r="B42" t="n">
-        <v>3011</v>
+        <v>23</v>
       </c>
       <c r="C42" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="D42" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="E42" t="n">
-        <v>3012</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>3010</v>
+        <v>1123</v>
       </c>
       <c r="B43" t="n">
-        <v>3012</v>
+        <v>123</v>
       </c>
       <c r="C43" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="D43" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="E43" t="n">
-        <v>3013</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3011</v>
+        <v>1223</v>
       </c>
       <c r="B44" t="n">
-        <v>3013</v>
+        <v>223</v>
       </c>
       <c r="C44" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="D44" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="E44" t="n">
-        <v>3014</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3012</v>
+        <v>1323</v>
       </c>
       <c r="B45" t="n">
-        <v>3014</v>
+        <v>323</v>
       </c>
       <c r="C45" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="D45" t="n">
-        <v>3020</v>
+        <v>433</v>
       </c>
       <c r="E45" t="n">
-        <v>3015</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3013</v>
+        <v>1033</v>
       </c>
       <c r="B46" t="n">
-        <v>3016</v>
+        <v>33</v>
       </c>
       <c r="C46" t="n">
-        <v>3021</v>
+        <v>43</v>
       </c>
       <c r="D46" t="n">
-        <v>3022</v>
+        <v>143</v>
       </c>
       <c r="E46" t="n">
-        <v>3017</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3014</v>
+        <v>1133</v>
       </c>
       <c r="B47" t="n">
-        <v>3017</v>
+        <v>133</v>
       </c>
       <c r="C47" t="n">
-        <v>3022</v>
+        <v>143</v>
       </c>
       <c r="D47" t="n">
-        <v>3023</v>
+        <v>243</v>
       </c>
       <c r="E47" t="n">
-        <v>3018</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>3015</v>
+        <v>1233</v>
       </c>
       <c r="B48" t="n">
-        <v>3018</v>
+        <v>233</v>
       </c>
       <c r="C48" t="n">
-        <v>3023</v>
+        <v>243</v>
       </c>
       <c r="D48" t="n">
-        <v>3024</v>
+        <v>343</v>
       </c>
       <c r="E48" t="n">
-        <v>3019</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3016</v>
+        <v>1333</v>
       </c>
       <c r="B49" t="n">
-        <v>3019</v>
+        <v>333</v>
       </c>
       <c r="C49" t="n">
-        <v>3024</v>
+        <v>343</v>
       </c>
       <c r="D49" t="n">
-        <v>3025</v>
+        <v>443</v>
       </c>
       <c r="E49" t="n">
-        <v>3020</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>4001</v>
+        <v>1004</v>
       </c>
       <c r="B50" t="n">
-        <v>4001</v>
+        <v>4</v>
       </c>
       <c r="C50" t="n">
-        <v>4006</v>
+        <v>14</v>
       </c>
       <c r="D50" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="E50" t="n">
-        <v>4002</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Stairs</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>4002</v>
+        <v>1104</v>
       </c>
       <c r="B51" t="n">
-        <v>4002</v>
+        <v>104</v>
       </c>
       <c r="C51" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="D51" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="E51" t="n">
-        <v>4003</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4003</v>
+        <v>1204</v>
       </c>
       <c r="B52" t="n">
-        <v>4003</v>
+        <v>204</v>
       </c>
       <c r="C52" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="D52" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="E52" t="n">
-        <v>4004</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>4004</v>
+        <v>1304</v>
       </c>
       <c r="B53" t="n">
-        <v>4004</v>
+        <v>304</v>
       </c>
       <c r="C53" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="D53" t="n">
-        <v>4010</v>
+        <v>414</v>
       </c>
       <c r="E53" t="n">
-        <v>4005</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4005</v>
+        <v>1014</v>
       </c>
       <c r="B54" t="n">
-        <v>4006</v>
+        <v>14</v>
       </c>
       <c r="C54" t="n">
-        <v>4011</v>
+        <v>24</v>
       </c>
       <c r="D54" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="E54" t="n">
-        <v>4007</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>4006</v>
+        <v>1114</v>
       </c>
       <c r="B55" t="n">
-        <v>4007</v>
+        <v>114</v>
       </c>
       <c r="C55" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="D55" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="E55" t="n">
-        <v>4008</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>4007</v>
+        <v>1214</v>
       </c>
       <c r="B56" t="n">
-        <v>4008</v>
+        <v>214</v>
       </c>
       <c r="C56" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="D56" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="E56" t="n">
-        <v>4009</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4008</v>
+        <v>1314</v>
       </c>
       <c r="B57" t="n">
-        <v>4009</v>
+        <v>314</v>
       </c>
       <c r="C57" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="D57" t="n">
-        <v>4015</v>
+        <v>424</v>
       </c>
       <c r="E57" t="n">
-        <v>4010</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>4009</v>
+        <v>1024</v>
       </c>
       <c r="B58" t="n">
-        <v>4011</v>
+        <v>24</v>
       </c>
       <c r="C58" t="n">
-        <v>4016</v>
+        <v>34</v>
       </c>
       <c r="D58" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="E58" t="n">
-        <v>4012</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>4010</v>
+        <v>1124</v>
       </c>
       <c r="B59" t="n">
-        <v>4012</v>
+        <v>124</v>
       </c>
       <c r="C59" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="D59" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="E59" t="n">
-        <v>4013</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4011</v>
+        <v>1224</v>
       </c>
       <c r="B60" t="n">
-        <v>4013</v>
+        <v>224</v>
       </c>
       <c r="C60" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="D60" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="E60" t="n">
-        <v>4014</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4012</v>
+        <v>1324</v>
       </c>
       <c r="B61" t="n">
-        <v>4014</v>
+        <v>324</v>
       </c>
       <c r="C61" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="D61" t="n">
-        <v>4020</v>
+        <v>434</v>
       </c>
       <c r="E61" t="n">
-        <v>4015</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>4013</v>
+        <v>1034</v>
       </c>
       <c r="B62" t="n">
-        <v>4016</v>
+        <v>34</v>
       </c>
       <c r="C62" t="n">
-        <v>4021</v>
+        <v>44</v>
       </c>
       <c r="D62" t="n">
-        <v>4022</v>
+        <v>144</v>
       </c>
       <c r="E62" t="n">
-        <v>4017</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4014</v>
+        <v>1134</v>
       </c>
       <c r="B63" t="n">
-        <v>4017</v>
+        <v>134</v>
       </c>
       <c r="C63" t="n">
-        <v>4022</v>
+        <v>144</v>
       </c>
       <c r="D63" t="n">
-        <v>4023</v>
+        <v>244</v>
       </c>
       <c r="E63" t="n">
-        <v>4018</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4015</v>
+        <v>1234</v>
       </c>
       <c r="B64" t="n">
-        <v>4018</v>
+        <v>234</v>
       </c>
       <c r="C64" t="n">
-        <v>4023</v>
+        <v>244</v>
       </c>
       <c r="D64" t="n">
-        <v>4024</v>
+        <v>344</v>
       </c>
       <c r="E64" t="n">
-        <v>4019</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4016</v>
+        <v>1334</v>
       </c>
       <c r="B65" t="n">
-        <v>4019</v>
+        <v>334</v>
       </c>
       <c r="C65" t="n">
-        <v>4024</v>
+        <v>344</v>
       </c>
       <c r="D65" t="n">
-        <v>4025</v>
+        <v>444</v>
       </c>
       <c r="E65" t="n">
-        <v>4020</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>rectangle-tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3001</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4001</v>
-      </c>
+        <v>434</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Slab</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
